--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0002T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0002T0006Z000C1N14_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.1446350569403</v>
+        <v>6.686003196752799</v>
       </c>
       <c r="D2" t="n">
-        <v>40.86074961814428</v>
+        <v>6.639871812948446</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
